--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.54773974927584</v>
+        <v>5.614007709257325</v>
       </c>
       <c r="D2" t="n">
-        <v>34.41500149981663</v>
+        <v>5.592437743720202</v>
       </c>
       <c r="E2" t="n">
-        <v>6.587394430181551</v>
+        <v>1.070451594904502</v>
       </c>
       <c r="F2" t="n">
-        <v>6.538451631650836</v>
+        <v>1.062498390143261</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74000377933967</v>
+        <v>4.020250614142697</v>
       </c>
       <c r="D3" t="n">
-        <v>24.8093169911045</v>
+        <v>4.03151401105448</v>
       </c>
       <c r="E3" t="n">
-        <v>6.587394430181551</v>
+        <v>1.070451594904502</v>
       </c>
       <c r="F3" t="n">
-        <v>6.538451631650836</v>
+        <v>1.062498390143261</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.02233266307369</v>
+        <v>4.553629057749474</v>
       </c>
       <c r="D4" t="n">
-        <v>28.14011048783166</v>
+        <v>4.572767954272644</v>
       </c>
       <c r="E4" t="n">
-        <v>6.587394430181551</v>
+        <v>1.070451594904502</v>
       </c>
       <c r="F4" t="n">
-        <v>6.538451631650836</v>
+        <v>1.062498390143261</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.84602079143549</v>
+        <v>3.387478378608268</v>
       </c>
       <c r="D5" t="n">
-        <v>20.97334733086942</v>
+        <v>3.408168941266281</v>
       </c>
       <c r="E5" t="n">
-        <v>6.587394430181551</v>
+        <v>1.070451594904502</v>
       </c>
       <c r="F5" t="n">
-        <v>6.538451631650836</v>
+        <v>1.062498390143261</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.81725791093053</v>
+        <v>2.732804410526211</v>
       </c>
       <c r="D6" t="n">
-        <v>16.94953336804014</v>
+        <v>2.754299172306523</v>
       </c>
       <c r="E6" t="n">
-        <v>6.587394430181551</v>
+        <v>1.070451594904502</v>
       </c>
       <c r="F6" t="n">
-        <v>6.538451631650836</v>
+        <v>1.062498390143261</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.5312424270433</v>
+        <v>5.611326894394535</v>
       </c>
       <c r="D7" t="n">
-        <v>34.66756636594095</v>
+        <v>5.633479534465405</v>
       </c>
       <c r="E7" t="n">
-        <v>6.587394430181551</v>
+        <v>1.070451594904502</v>
       </c>
       <c r="F7" t="n">
-        <v>6.538451631650836</v>
+        <v>1.062498390143261</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
